--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2021/OKLAHOMA_2021.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2021/OKLAHOMA_2021.xlsx
@@ -463,7 +463,7 @@
         <v>6</v>
       </c>
       <c r="D6">
-        <v>0.0009376465072667605</v>
+        <v>0.0009376465072667604</v>
       </c>
     </row>
     <row r="7">
@@ -571,7 +571,7 @@
         <v>6</v>
       </c>
       <c r="D12">
-        <v>0.0009376465072667605</v>
+        <v>0.0009376465072667604</v>
       </c>
     </row>
     <row r="13">
@@ -859,7 +859,7 @@
         <v>6</v>
       </c>
       <c r="D28">
-        <v>0.0009376465072667605</v>
+        <v>0.0009376465072667604</v>
       </c>
     </row>
     <row r="29">
@@ -1543,7 +1543,7 @@
         <v>6</v>
       </c>
       <c r="D66">
-        <v>0.0009376465072667605</v>
+        <v>0.0009376465072667604</v>
       </c>
     </row>
     <row r="67">
@@ -1867,7 +1867,7 @@
         <v>6</v>
       </c>
       <c r="D84">
-        <v>0.0009376465072667605</v>
+        <v>0.0009376465072667604</v>
       </c>
     </row>
     <row r="85">
@@ -2274,7 +2274,7 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Cuatro Cienegas</t>
+          <t>Cuatrocienegas</t>
         </is>
       </c>
       <c r="C107">
@@ -2443,7 +2443,7 @@
         <v>6</v>
       </c>
       <c r="D116">
-        <v>0.0009376465072667605</v>
+        <v>0.0009376465072667604</v>
       </c>
     </row>
     <row r="117">
@@ -2785,7 +2785,7 @@
         <v>6</v>
       </c>
       <c r="D135">
-        <v>0.0009376465072667605</v>
+        <v>0.0009376465072667604</v>
       </c>
     </row>
     <row r="136">
@@ -2976,7 +2976,7 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>General Simon Bolivar</t>
+          <t>Gral. Simon Bolivar</t>
         </is>
       </c>
       <c r="C146">
@@ -3127,7 +3127,7 @@
         <v>6</v>
       </c>
       <c r="D154">
-        <v>0.0009376465072667605</v>
+        <v>0.0009376465072667604</v>
       </c>
     </row>
     <row r="155">
@@ -3163,7 +3163,7 @@
         <v>6</v>
       </c>
       <c r="D156">
-        <v>0.0009376465072667605</v>
+        <v>0.0009376465072667604</v>
       </c>
     </row>
     <row r="157">
@@ -3181,7 +3181,7 @@
         <v>6</v>
       </c>
       <c r="D157">
-        <v>0.0009376465072667605</v>
+        <v>0.0009376465072667604</v>
       </c>
     </row>
     <row r="158">
@@ -4225,7 +4225,7 @@
         <v>6</v>
       </c>
       <c r="D215">
-        <v>0.0009376465072667605</v>
+        <v>0.0009376465072667604</v>
       </c>
     </row>
     <row r="216">
@@ -4344,7 +4344,7 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>Allende</t>
+          <t>San Miguel De Allende</t>
         </is>
       </c>
       <c r="C222">
@@ -4506,7 +4506,7 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C231">
@@ -5161,7 +5161,7 @@
         <v>6</v>
       </c>
       <c r="D267">
-        <v>0.0009376465072667605</v>
+        <v>0.0009376465072667604</v>
       </c>
     </row>
     <row r="268">
@@ -5863,7 +5863,7 @@
         <v>6</v>
       </c>
       <c r="D306">
-        <v>0.0009376465072667605</v>
+        <v>0.0009376465072667604</v>
       </c>
     </row>
     <row r="307">
@@ -6277,7 +6277,7 @@
         <v>6</v>
       </c>
       <c r="D329">
-        <v>0.0009376465072667605</v>
+        <v>0.0009376465072667604</v>
       </c>
     </row>
     <row r="330">
@@ -6475,7 +6475,7 @@
         <v>6</v>
       </c>
       <c r="D340">
-        <v>0.0009376465072667605</v>
+        <v>0.0009376465072667604</v>
       </c>
     </row>
     <row r="341">
@@ -7123,7 +7123,7 @@
         <v>6</v>
       </c>
       <c r="D376">
-        <v>0.0009376465072667605</v>
+        <v>0.0009376465072667604</v>
       </c>
     </row>
     <row r="377">
@@ -8005,7 +8005,7 @@
         <v>6</v>
       </c>
       <c r="D425">
-        <v>0.0009376465072667605</v>
+        <v>0.0009376465072667604</v>
       </c>
     </row>
     <row r="426">
@@ -8131,7 +8131,7 @@
         <v>6</v>
       </c>
       <c r="D432">
-        <v>0.0009376465072667605</v>
+        <v>0.0009376465072667604</v>
       </c>
     </row>
     <row r="433">
@@ -8239,7 +8239,7 @@
         <v>6</v>
       </c>
       <c r="D438">
-        <v>0.0009376465072667605</v>
+        <v>0.0009376465072667604</v>
       </c>
     </row>
     <row r="439">
@@ -9463,7 +9463,7 @@
         <v>6</v>
       </c>
       <c r="D506">
-        <v>0.0009376465072667605</v>
+        <v>0.0009376465072667604</v>
       </c>
     </row>
     <row r="507">
@@ -9535,7 +9535,7 @@
         <v>6</v>
       </c>
       <c r="D510">
-        <v>0.0009376465072667605</v>
+        <v>0.0009376465072667604</v>
       </c>
     </row>
     <row r="511">
@@ -9553,7 +9553,7 @@
         <v>6</v>
       </c>
       <c r="D511">
-        <v>0.0009376465072667605</v>
+        <v>0.0009376465072667604</v>
       </c>
     </row>
     <row r="512">
@@ -9679,7 +9679,7 @@
         <v>6</v>
       </c>
       <c r="D518">
-        <v>0.0009376465072667605</v>
+        <v>0.0009376465072667604</v>
       </c>
     </row>
     <row r="519">
@@ -9942,7 +9942,7 @@
       </c>
       <c r="B533" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 22 -</t>
+          <t>San Pedro Mixtepec -Dto. 22 -</t>
         </is>
       </c>
       <c r="C533">
@@ -11407,7 +11407,7 @@
         <v>6</v>
       </c>
       <c r="D614">
-        <v>0.0009376465072667605</v>
+        <v>0.0009376465072667604</v>
       </c>
     </row>
     <row r="615">
@@ -11551,7 +11551,7 @@
         <v>6</v>
       </c>
       <c r="D622">
-        <v>0.0009376465072667605</v>
+        <v>0.0009376465072667604</v>
       </c>
     </row>
     <row r="623">
@@ -11965,7 +11965,7 @@
         <v>59</v>
       </c>
       <c r="D645">
-        <v>0.009220190654789811</v>
+        <v>0.009220190654789812</v>
       </c>
     </row>
     <row r="646">
@@ -12577,7 +12577,7 @@
         <v>6</v>
       </c>
       <c r="D679">
-        <v>0.0009376465072667605</v>
+        <v>0.0009376465072667604</v>
       </c>
     </row>
     <row r="680">
@@ -12613,7 +12613,7 @@
         <v>6</v>
       </c>
       <c r="D681">
-        <v>0.0009376465072667605</v>
+        <v>0.0009376465072667604</v>
       </c>
     </row>
     <row r="682">
@@ -13279,7 +13279,7 @@
         <v>6</v>
       </c>
       <c r="D718">
-        <v>0.0009376465072667605</v>
+        <v>0.0009376465072667604</v>
       </c>
     </row>
     <row r="719">
@@ -13711,7 +13711,7 @@
         <v>6</v>
       </c>
       <c r="D742">
-        <v>0.0009376465072667605</v>
+        <v>0.0009376465072667604</v>
       </c>
     </row>
     <row r="743">
@@ -14557,7 +14557,7 @@
         <v>6</v>
       </c>
       <c r="D789">
-        <v>0.0009376465072667605</v>
+        <v>0.0009376465072667604</v>
       </c>
     </row>
     <row r="790">
@@ -15079,7 +15079,7 @@
         <v>6</v>
       </c>
       <c r="D818">
-        <v>0.0009376465072667605</v>
+        <v>0.0009376465072667604</v>
       </c>
     </row>
     <row r="819">
